--- a/automation/reports/Excel/Automation_Test_Report.xlsx
+++ b/automation/reports/Excel/Automation_Test_Report.xlsx
@@ -3701,7 +3701,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>981</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3721,7 +3721,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>933</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3741,7 +3741,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>823</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3761,7 +3761,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>535</v>
+        <v>815</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3781,7 +3781,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>359</v>
+        <v>919</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3801,7 +3801,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>633</v>
+        <v>931</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3821,7 +3821,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>682</v>
+        <v>961</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3841,7 +3841,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>213</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3861,7 +3861,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>833</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3881,7 +3881,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>704</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3901,7 +3901,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>223</v>
+        <v>636</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3921,7 +3921,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>410</v>
+        <v>753</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3941,7 +3941,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>831</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3961,7 +3961,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>868</v>
+        <v>835</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3981,7 +3981,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>678</v>
+        <v>712</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4001,7 +4001,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>906</v>
+        <v>563</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4021,7 +4021,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>524</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4041,7 +4041,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>541</v>
+        <v>837</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4061,7 +4061,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>285</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4081,7 +4081,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>631</v>
+        <v>807</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4101,7 +4101,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>876</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4121,7 +4121,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>374</v>
+        <v>999</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -4141,7 +4141,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>626</v>
+        <v>487</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -4161,7 +4161,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>352</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4181,7 +4181,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>268</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4201,7 +4201,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4221,7 +4221,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4241,7 +4241,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>318</v>
+        <v>923</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -4261,7 +4261,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>773</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4281,7 +4281,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>575</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -4301,7 +4301,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>373</v>
+        <v>558</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -4321,7 +4321,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>321</v>
+        <v>684</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4341,7 +4341,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>537</v>
+        <v>459</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4361,7 +4361,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>498</v>
+        <v>439</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4381,7 +4381,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>243</v>
+        <v>793</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4401,7 +4401,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>799</v>
+        <v>843</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>893</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -4441,7 +4441,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>215</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4461,7 +4461,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>454</v>
+        <v>387</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -4481,7 +4481,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>534</v>
+        <v>644</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -4501,7 +4501,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>759</v>
+        <v>780</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -4521,7 +4521,7 @@
         <v>10</v>
       </c>
       <c r="F43">
-        <v>848</v>
+        <v>673</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -4541,7 +4541,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>676</v>
+        <v>911</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -4561,7 +4561,7 @@
         <v>10</v>
       </c>
       <c r="F45">
-        <v>980</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>857</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -4601,7 +4601,7 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>502</v>
+        <v>405</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -4621,7 +4621,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>317</v>
+        <v>511</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4641,7 +4641,7 @@
         <v>10</v>
       </c>
       <c r="F49">
-        <v>291</v>
+        <v>368</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4661,7 +4661,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>498</v>
+        <v>934</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4681,7 +4681,7 @@
         <v>10</v>
       </c>
       <c r="F51">
-        <v>504</v>
+        <v>599</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4701,7 +4701,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>629</v>
+        <v>878</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4721,7 +4721,7 @@
         <v>10</v>
       </c>
       <c r="F53">
-        <v>575</v>
+        <v>605</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4741,7 +4741,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>750</v>
+        <v>981</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4761,7 +4761,7 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>910</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4781,7 +4781,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>492</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4801,7 +4801,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>870</v>
+        <v>788</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -4841,7 +4841,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>489</v>
+        <v>684</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -4861,7 +4861,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>536</v>
+        <v>414</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -4881,7 +4881,7 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>731</v>
+        <v>679</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4901,7 +4901,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>405</v>
+        <v>953</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -4921,7 +4921,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>537</v>
+        <v>910</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -4941,7 +4941,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>434</v>
+        <v>261</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4961,7 +4961,7 @@
         <v>10</v>
       </c>
       <c r="F65">
-        <v>789</v>
+        <v>590</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4981,7 +4981,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>953</v>
+        <v>547</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -5001,7 +5001,7 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>723</v>
+        <v>513</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -5021,7 +5021,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>483</v>
+        <v>409</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -5041,7 +5041,7 @@
         <v>10</v>
       </c>
       <c r="F69">
-        <v>790</v>
+        <v>569</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -5061,7 +5061,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>441</v>
+        <v>382</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -5081,7 +5081,7 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>360</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -5101,7 +5101,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>415</v>
+        <v>356</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -5121,7 +5121,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>478</v>
+        <v>914</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -5141,7 +5141,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>653</v>
+        <v>566</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -5161,7 +5161,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>404</v>
+        <v>966</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -5181,7 +5181,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>495</v>
+        <v>887</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5201,7 +5201,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>302</v>
+        <v>552</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -5221,7 +5221,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>269</v>
+        <v>625</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -5241,7 +5241,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>300</v>
+        <v>899</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>719</v>
+        <v>585</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -5281,7 +5281,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>457</v>
+        <v>565</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -5301,7 +5301,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>479</v>
+        <v>914</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -5321,7 +5321,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>837</v>
+        <v>709</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5341,7 +5341,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>661</v>
+        <v>382</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>908</v>
+        <v>574</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -5381,7 +5381,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>346</v>
+        <v>922</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -5401,7 +5401,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>703</v>
+        <v>769</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -5421,7 +5421,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>990</v>
+        <v>504</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -5441,7 +5441,7 @@
         <v>10</v>
       </c>
       <c r="F89">
-        <v>338</v>
+        <v>554</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -5461,7 +5461,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>778</v>
+        <v>910</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -5481,7 +5481,7 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>255</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -5501,7 +5501,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>266</v>
+        <v>785</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -5521,7 +5521,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>411</v>
+        <v>747</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -5541,7 +5541,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>911</v>
+        <v>471</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -5561,7 +5561,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>445</v>
+        <v>885</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -5581,7 +5581,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>220</v>
+        <v>946</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>655</v>
+        <v>616</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -5621,7 +5621,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>279</v>
+        <v>514</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -5641,7 +5641,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>536</v>
+        <v>950</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -5661,7 +5661,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>558</v>
+        <v>904</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -5681,7 +5681,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>507</v>
+        <v>434</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -5701,7 +5701,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -5721,7 +5721,7 @@
         <v>10</v>
       </c>
       <c r="F103">
-        <v>684</v>
+        <v>390</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -5741,7 +5741,7 @@
         <v>10</v>
       </c>
       <c r="F104">
-        <v>342</v>
+        <v>798</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -5761,7 +5761,7 @@
         <v>10</v>
       </c>
       <c r="F105">
-        <v>968</v>
+        <v>834</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -5781,7 +5781,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>901</v>
+        <v>880</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -5801,7 +5801,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>311</v>
+        <v>430</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -5821,7 +5821,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>838</v>
+        <v>767</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -5841,7 +5841,7 @@
         <v>10</v>
       </c>
       <c r="F109">
-        <v>687</v>
+        <v>711</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -5861,7 +5861,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>672</v>
+        <v>642</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5881,7 +5881,7 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>785</v>
+        <v>947</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -5901,7 +5901,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>414</v>
+        <v>232</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -5921,7 +5921,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>459</v>
+        <v>359</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -5941,7 +5941,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>947</v>
+        <v>351</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -5961,7 +5961,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>523</v>
+        <v>833</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -5981,7 +5981,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>899</v>
+        <v>916</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -6001,7 +6001,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>221</v>
+        <v>877</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -6021,7 +6021,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>744</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -6041,7 +6041,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>408</v>
+        <v>381</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -6061,7 +6061,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>520</v>
+        <v>945</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -6081,7 +6081,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>265</v>
+        <v>917</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -6101,7 +6101,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>253</v>
+        <v>719</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -6121,7 +6121,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>867</v>
+        <v>939</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -6141,7 +6141,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>281</v>
+        <v>983</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -6161,7 +6161,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>776</v>
+        <v>612</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -6181,7 +6181,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>786</v>
+        <v>551</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -6201,7 +6201,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>566</v>
+        <v>806</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -6221,7 +6221,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>444</v>
+        <v>312</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6241,7 +6241,7 @@
         <v>10</v>
       </c>
       <c r="F129">
-        <v>448</v>
+        <v>435</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -6261,7 +6261,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>685</v>
+        <v>526</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -6281,7 +6281,7 @@
         <v>10</v>
       </c>
       <c r="F131">
-        <v>747</v>
+        <v>338</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -6301,7 +6301,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>613</v>
+        <v>508</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -6321,7 +6321,7 @@
         <v>10</v>
       </c>
       <c r="F133">
-        <v>493</v>
+        <v>613</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -6341,7 +6341,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>337</v>
+        <v>874</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -6361,7 +6361,7 @@
         <v>10</v>
       </c>
       <c r="F135">
-        <v>754</v>
+        <v>784</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -6381,7 +6381,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>778</v>
+        <v>894</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -6401,7 +6401,7 @@
         <v>10</v>
       </c>
       <c r="F137">
-        <v>689</v>
+        <v>521</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -6421,7 +6421,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>870</v>
+        <v>622</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -6441,7 +6441,7 @@
         <v>10</v>
       </c>
       <c r="F139">
-        <v>643</v>
+        <v>722</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -6461,7 +6461,7 @@
         <v>10</v>
       </c>
       <c r="F140">
-        <v>943</v>
+        <v>743</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -6481,7 +6481,7 @@
         <v>10</v>
       </c>
       <c r="F141">
-        <v>854</v>
+        <v>497</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -6501,7 +6501,7 @@
         <v>10</v>
       </c>
       <c r="F142">
-        <v>989</v>
+        <v>999</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -6521,7 +6521,7 @@
         <v>10</v>
       </c>
       <c r="F143">
-        <v>643</v>
+        <v>553</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -6541,7 +6541,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>786</v>
+        <v>536</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -6561,7 +6561,7 @@
         <v>10</v>
       </c>
       <c r="F145">
-        <v>556</v>
+        <v>570</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -6581,7 +6581,7 @@
         <v>10</v>
       </c>
       <c r="F146">
-        <v>796</v>
+        <v>771</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -6601,7 +6601,7 @@
         <v>10</v>
       </c>
       <c r="F147">
-        <v>790</v>
+        <v>681</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -6621,7 +6621,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>987</v>
+        <v>427</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -6641,7 +6641,7 @@
         <v>10</v>
       </c>
       <c r="F149">
-        <v>724</v>
+        <v>520</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -6661,7 +6661,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -6681,7 +6681,7 @@
         <v>10</v>
       </c>
       <c r="F151">
-        <v>244</v>
+        <v>202</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -6701,7 +6701,7 @@
         <v>10</v>
       </c>
       <c r="F152">
-        <v>714</v>
+        <v>431</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -6721,7 +6721,7 @@
         <v>10</v>
       </c>
       <c r="F153">
-        <v>298</v>
+        <v>849</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -6741,7 +6741,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>278</v>
+        <v>673</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -6761,7 +6761,7 @@
         <v>10</v>
       </c>
       <c r="F155">
-        <v>838</v>
+        <v>982</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -6781,7 +6781,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>577</v>
+        <v>683</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -6801,7 +6801,7 @@
         <v>10</v>
       </c>
       <c r="F157">
-        <v>632</v>
+        <v>670</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -6821,7 +6821,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>444</v>
+        <v>278</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -6841,7 +6841,7 @@
         <v>10</v>
       </c>
       <c r="F159">
-        <v>668</v>
+        <v>599</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -6861,7 +6861,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>457</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -6881,7 +6881,7 @@
         <v>10</v>
       </c>
       <c r="F161">
-        <v>467</v>
+        <v>259</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -6901,7 +6901,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>214</v>
+        <v>303</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -6921,7 +6921,7 @@
         <v>10</v>
       </c>
       <c r="F163">
-        <v>881</v>
+        <v>671</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -6941,7 +6941,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>992</v>
+        <v>827</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -6961,7 +6961,7 @@
         <v>10</v>
       </c>
       <c r="F165">
-        <v>829</v>
+        <v>258</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6981,7 +6981,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -7001,7 +7001,7 @@
         <v>10</v>
       </c>
       <c r="F167">
-        <v>583</v>
+        <v>494</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -7021,7 +7021,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>900</v>
+        <v>807</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -7041,7 +7041,7 @@
         <v>10</v>
       </c>
       <c r="F169">
-        <v>727</v>
+        <v>482</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -7061,7 +7061,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>686</v>
+        <v>356</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -7081,7 +7081,7 @@
         <v>10</v>
       </c>
       <c r="F171">
-        <v>237</v>
+        <v>443</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -7101,7 +7101,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>867</v>
+        <v>294</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -7121,7 +7121,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>397</v>
+        <v>723</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -7141,7 +7141,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>868</v>
+        <v>620</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -7161,7 +7161,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>336</v>
+        <v>567</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -7181,7 +7181,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>572</v>
+        <v>616</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -7201,7 +7201,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>398</v>
+        <v>377</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -7221,7 +7221,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>394</v>
+        <v>870</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -7241,7 +7241,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>832</v>
+        <v>463</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -7261,7 +7261,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>397</v>
+        <v>522</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -7281,7 +7281,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>494</v>
+        <v>365</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -7301,7 +7301,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>457</v>
+        <v>211</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -7321,7 +7321,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>596</v>
+        <v>685</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -7341,7 +7341,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>613</v>
+        <v>253</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -7361,7 +7361,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>294</v>
+        <v>674</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -7381,7 +7381,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>527</v>
+        <v>258</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -7401,7 +7401,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>659</v>
+        <v>402</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -7421,7 +7421,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>962</v>
+        <v>784</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -7441,7 +7441,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>499</v>
+        <v>205</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -7461,7 +7461,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>255</v>
+        <v>771</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -7481,7 +7481,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>384</v>
+        <v>415</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -7501,7 +7501,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>431</v>
+        <v>406</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -7521,7 +7521,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>887</v>
+        <v>483</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -7541,7 +7541,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>858</v>
+        <v>399</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -7561,7 +7561,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>452</v>
+        <v>936</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -7581,7 +7581,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>886</v>
+        <v>978</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -7601,7 +7601,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>958</v>
+        <v>920</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -7621,7 +7621,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>360</v>
+        <v>431</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -7641,7 +7641,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>449</v>
+        <v>957</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -7661,7 +7661,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>832</v>
+        <v>248</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -7681,7 +7681,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>939</v>
+        <v>559</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -7701,7 +7701,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>310</v>
+        <v>587</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -7721,7 +7721,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>285</v>
+        <v>444</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -7741,7 +7741,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>637</v>
+        <v>261</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -7761,7 +7761,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>687</v>
+        <v>292</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -7781,7 +7781,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>382</v>
+        <v>837</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -7801,7 +7801,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>961</v>
+        <v>530</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -7821,7 +7821,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>279</v>
+        <v>803</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -7841,7 +7841,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>276</v>
+        <v>922</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -7861,7 +7861,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>801</v>
+        <v>511</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -7881,7 +7881,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>534</v>
+        <v>442</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -7901,7 +7901,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>857</v>
+        <v>231</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -7921,7 +7921,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>820</v>
+        <v>616</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -7941,7 +7941,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>799</v>
+        <v>660</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -7961,7 +7961,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>573</v>
+        <v>553</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>599</v>
+        <v>230</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -8001,7 +8001,7 @@
         <v>10</v>
       </c>
       <c r="F217">
-        <v>435</v>
+        <v>413</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -8021,7 +8021,7 @@
         <v>10</v>
       </c>
       <c r="F218">
-        <v>596</v>
+        <v>620</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -8041,7 +8041,7 @@
         <v>10</v>
       </c>
       <c r="F219">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -8061,7 +8061,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>612</v>
+        <v>332</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -8081,7 +8081,7 @@
         <v>10</v>
       </c>
       <c r="F221">
-        <v>763</v>
+        <v>342</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -8101,7 +8101,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>517</v>
+        <v>479</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -8121,7 +8121,7 @@
         <v>10</v>
       </c>
       <c r="F223">
-        <v>782</v>
+        <v>207</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -8141,7 +8141,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>777</v>
+        <v>788</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -8161,7 +8161,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>399</v>
+        <v>425</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -8181,7 +8181,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>964</v>
+        <v>776</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -8201,7 +8201,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>398</v>
+        <v>959</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -8221,7 +8221,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>750</v>
+        <v>831</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -8241,7 +8241,7 @@
         <v>10</v>
       </c>
       <c r="F229">
-        <v>911</v>
+        <v>868</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -8261,7 +8261,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>392</v>
+        <v>571</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -8281,7 +8281,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>308</v>
+        <v>467</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -8301,7 +8301,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>534</v>
+        <v>750</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -8321,7 +8321,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>451</v>
+        <v>297</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -8341,7 +8341,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>665</v>
+        <v>328</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -8361,7 +8361,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>391</v>
+        <v>829</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -8381,7 +8381,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>666</v>
+        <v>950</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -8401,7 +8401,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>770</v>
+        <v>847</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -8421,7 +8421,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>718</v>
+        <v>967</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -8441,7 +8441,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>613</v>
+        <v>968</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -8461,7 +8461,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>767</v>
+        <v>759</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -8481,7 +8481,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>493</v>
+        <v>889</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -8501,7 +8501,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>518</v>
+        <v>281</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -8521,7 +8521,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>822</v>
+        <v>689</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -8541,7 +8541,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>630</v>
+        <v>857</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -8561,7 +8561,7 @@
         <v>10</v>
       </c>
       <c r="F245">
-        <v>862</v>
+        <v>293</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -8581,7 +8581,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>296</v>
+        <v>558</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -8601,7 +8601,7 @@
         <v>10</v>
       </c>
       <c r="F247">
-        <v>806</v>
+        <v>903</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -8621,7 +8621,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>484</v>
+        <v>268</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -8641,7 +8641,7 @@
         <v>10</v>
       </c>
       <c r="F249">
-        <v>720</v>
+        <v>528</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -8661,7 +8661,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>590</v>
+        <v>734</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -8681,7 +8681,7 @@
         <v>10</v>
       </c>
       <c r="F251">
-        <v>468</v>
+        <v>229</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -8701,7 +8701,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>333</v>
+        <v>601</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -8721,7 +8721,7 @@
         <v>10</v>
       </c>
       <c r="F253">
-        <v>327</v>
+        <v>683</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -8741,7 +8741,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>609</v>
+        <v>922</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -8761,7 +8761,7 @@
         <v>10</v>
       </c>
       <c r="F255">
-        <v>638</v>
+        <v>946</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -8781,7 +8781,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>306</v>
+        <v>780</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -8801,7 +8801,7 @@
         <v>10</v>
       </c>
       <c r="F257">
-        <v>657</v>
+        <v>514</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -8821,7 +8821,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>305</v>
+        <v>205</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -8841,7 +8841,7 @@
         <v>10</v>
       </c>
       <c r="F259">
-        <v>594</v>
+        <v>682</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -8861,7 +8861,7 @@
         <v>10</v>
       </c>
       <c r="F260">
-        <v>927</v>
+        <v>433</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -8881,7 +8881,7 @@
         <v>10</v>
       </c>
       <c r="F261">
-        <v>746</v>
+        <v>691</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -8901,7 +8901,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>771</v>
+        <v>725</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -8921,7 +8921,7 @@
         <v>10</v>
       </c>
       <c r="F263">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -8941,7 +8941,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>998</v>
+        <v>830</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -8961,7 +8961,7 @@
         <v>10</v>
       </c>
       <c r="F265">
-        <v>723</v>
+        <v>987</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -8981,7 +8981,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>214</v>
+        <v>947</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -9001,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="F267">
-        <v>579</v>
+        <v>970</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -9021,7 +9021,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>564</v>
+        <v>737</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -9041,7 +9041,7 @@
         <v>10</v>
       </c>
       <c r="F269">
-        <v>636</v>
+        <v>394</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -9061,7 +9061,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>547</v>
+        <v>861</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -9081,7 +9081,7 @@
         <v>10</v>
       </c>
       <c r="F271">
-        <v>933</v>
+        <v>468</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -9101,7 +9101,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>996</v>
+        <v>669</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -9121,7 +9121,7 @@
         <v>10</v>
       </c>
       <c r="F273">
-        <v>749</v>
+        <v>396</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -9141,7 +9141,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>995</v>
+        <v>449</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -9161,7 +9161,7 @@
         <v>10</v>
       </c>
       <c r="F275">
-        <v>747</v>
+        <v>478</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -9181,7 +9181,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>465</v>
+        <v>544</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -9201,7 +9201,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>892</v>
+        <v>222</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -9221,7 +9221,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>387</v>
+        <v>595</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -9241,7 +9241,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>543</v>
+        <v>983</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -9261,7 +9261,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>404</v>
+        <v>681</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -9281,7 +9281,7 @@
         <v>10</v>
       </c>
       <c r="F281">
-        <v>651</v>
+        <v>268</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -9301,7 +9301,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>739</v>
+        <v>298</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -9321,7 +9321,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>825</v>
+        <v>770</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>394</v>
+        <v>497</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -9361,7 +9361,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>656</v>
+        <v>862</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -9381,7 +9381,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>722</v>
+        <v>318</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -9401,7 +9401,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>712</v>
+        <v>732</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -9421,7 +9421,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>814</v>
+        <v>492</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -9441,7 +9441,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>602</v>
+        <v>367</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -9461,7 +9461,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>804</v>
+        <v>828</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -9481,7 +9481,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>967</v>
+        <v>344</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -9501,7 +9501,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>624</v>
+        <v>906</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -9521,7 +9521,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>358</v>
+        <v>384</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -9541,7 +9541,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>750</v>
+        <v>660</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -9561,7 +9561,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>622</v>
+        <v>755</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -9581,7 +9581,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>713</v>
+        <v>875</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -9601,7 +9601,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>815</v>
+        <v>252</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -9621,7 +9621,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>258</v>
+        <v>507</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -9641,7 +9641,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>417</v>
+        <v>591</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -9661,7 +9661,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>206</v>
+        <v>347</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -9681,7 +9681,7 @@
         <v>10</v>
       </c>
       <c r="F301">
-        <v>201</v>
+        <v>584</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -9701,7 +9701,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>995</v>
+        <v>751</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -9721,7 +9721,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>292</v>
+        <v>822</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -9741,7 +9741,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>422</v>
+        <v>528</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -9761,7 +9761,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>714</v>
+        <v>773</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -9781,7 +9781,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>538</v>
+        <v>269</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -9801,7 +9801,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -9821,7 +9821,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -9841,7 +9841,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>839</v>
+        <v>345</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -9861,7 +9861,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>517</v>
+        <v>620</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -9881,7 +9881,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>904</v>
+        <v>719</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -9901,7 +9901,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>929</v>
+        <v>731</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -9921,7 +9921,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>997</v>
+        <v>257</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -9941,7 +9941,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>710</v>
+        <v>888</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -9961,7 +9961,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>583</v>
+        <v>767</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -9981,7 +9981,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>732</v>
+        <v>386</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -10001,7 +10001,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>340</v>
+        <v>253</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -10021,7 +10021,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>486</v>
+        <v>288</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -10041,7 +10041,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>601</v>
+        <v>946</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -10061,7 +10061,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>265</v>
+        <v>847</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -10081,7 +10081,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>864</v>
+        <v>390</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -10101,7 +10101,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>356</v>
+        <v>261</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -10121,7 +10121,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>307</v>
+        <v>371</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -10141,7 +10141,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>852</v>
+        <v>911</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -10161,7 +10161,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>207</v>
+        <v>950</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -10181,7 +10181,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>257</v>
+        <v>717</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -10201,7 +10201,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>205</v>
+        <v>228</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -10221,7 +10221,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>837</v>
+        <v>842</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -10241,7 +10241,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>494</v>
+        <v>355</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -10261,7 +10261,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>708</v>
+        <v>238</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -10281,7 +10281,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>480</v>
+        <v>777</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -10301,7 +10301,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>289</v>
+        <v>383</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -10321,7 +10321,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>971</v>
+        <v>479</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -10341,7 +10341,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>940</v>
+        <v>392</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -10361,7 +10361,7 @@
         <v>10</v>
       </c>
       <c r="F335">
-        <v>500</v>
+        <v>969</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -10381,7 +10381,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>666</v>
+        <v>211</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -10401,7 +10401,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>200</v>
+        <v>948</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -10421,7 +10421,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>896</v>
+        <v>341</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -10441,7 +10441,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>976</v>
+        <v>612</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -10461,7 +10461,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>748</v>
+        <v>616</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -10481,7 +10481,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>230</v>
+        <v>810</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -10501,7 +10501,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>353</v>
+        <v>701</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -10521,7 +10521,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>550</v>
+        <v>809</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -10541,7 +10541,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>622</v>
+        <v>968</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -10561,7 +10561,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>953</v>
+        <v>539</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -10581,7 +10581,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>820</v>
+        <v>748</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -10601,7 +10601,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>922</v>
+        <v>365</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -10621,7 +10621,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>756</v>
+        <v>857</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -10641,7 +10641,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>464</v>
+        <v>346</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -10661,7 +10661,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>612</v>
+        <v>790</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -10681,7 +10681,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>813</v>
+        <v>693</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -10701,7 +10701,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>264</v>
+        <v>951</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -10721,7 +10721,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>371</v>
+        <v>242</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -10741,7 +10741,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>655</v>
+        <v>932</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -10761,7 +10761,7 @@
         <v>10</v>
       </c>
       <c r="F355">
-        <v>811</v>
+        <v>952</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -10781,7 +10781,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>391</v>
+        <v>648</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -10801,7 +10801,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>222</v>
+        <v>402</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -10821,7 +10821,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>955</v>
+        <v>504</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -10841,7 +10841,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>738</v>
+        <v>973</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -10861,7 +10861,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>960</v>
+        <v>581</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -10881,7 +10881,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>754</v>
+        <v>762</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -10901,7 +10901,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>640</v>
+        <v>956</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -10921,7 +10921,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>871</v>
+        <v>337</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -10941,7 +10941,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>757</v>
+        <v>839</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -10961,7 +10961,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>520</v>
+        <v>672</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -10981,7 +10981,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>602</v>
+        <v>554</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -11001,7 +11001,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>951</v>
+        <v>520</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -11021,7 +11021,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>501</v>
+        <v>675</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>302</v>
+        <v>920</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -11061,7 +11061,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>829</v>
+        <v>615</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -11081,7 +11081,7 @@
         <v>10</v>
       </c>
       <c r="F371">
-        <v>423</v>
+        <v>517</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -11101,7 +11101,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>333</v>
+        <v>568</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -11121,7 +11121,7 @@
         <v>10</v>
       </c>
       <c r="F373">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -11141,7 +11141,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>981</v>
+        <v>768</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -11161,7 +11161,7 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>976</v>
+        <v>386</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -11181,7 +11181,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>334</v>
+        <v>522</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -11201,7 +11201,7 @@
         <v>10</v>
       </c>
       <c r="F377">
-        <v>268</v>
+        <v>556</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -11221,7 +11221,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>786</v>
+        <v>750</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -11241,7 +11241,7 @@
         <v>10</v>
       </c>
       <c r="F379">
-        <v>663</v>
+        <v>357</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -11261,7 +11261,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>251</v>
+        <v>898</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -11281,7 +11281,7 @@
         <v>10</v>
       </c>
       <c r="F381">
-        <v>756</v>
+        <v>559</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -11301,7 +11301,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>826</v>
+        <v>238</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -11321,7 +11321,7 @@
         <v>10</v>
       </c>
       <c r="F383">
-        <v>736</v>
+        <v>623</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -11341,7 +11341,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>322</v>
+        <v>585</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -11361,7 +11361,7 @@
         <v>10</v>
       </c>
       <c r="F385">
-        <v>684</v>
+        <v>315</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -11381,7 +11381,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>423</v>
+        <v>904</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -11401,7 +11401,7 @@
         <v>10</v>
       </c>
       <c r="F387">
-        <v>200</v>
+        <v>408</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -11421,7 +11421,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>411</v>
+        <v>483</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -11441,7 +11441,7 @@
         <v>10</v>
       </c>
       <c r="F389">
-        <v>388</v>
+        <v>488</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -11461,7 +11461,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>601</v>
+        <v>996</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -11481,7 +11481,7 @@
         <v>10</v>
       </c>
       <c r="F391">
-        <v>836</v>
+        <v>482</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -11501,7 +11501,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>798</v>
+        <v>879</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -11521,7 +11521,7 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>656</v>
+        <v>983</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -11541,7 +11541,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>676</v>
+        <v>265</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -11561,7 +11561,7 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>319</v>
+        <v>245</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -11581,7 +11581,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>811</v>
+        <v>268</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -11621,7 +11621,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>221</v>
+        <v>518</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -11641,7 +11641,7 @@
         <v>10</v>
       </c>
       <c r="F399">
-        <v>979</v>
+        <v>275</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -11661,7 +11661,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>845</v>
+        <v>327</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -11681,7 +11681,7 @@
         <v>10</v>
       </c>
       <c r="F401">
-        <v>782</v>
+        <v>308</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -11701,7 +11701,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>406</v>
+        <v>387</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="F403">
-        <v>758</v>
+        <v>251</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -11741,7 +11741,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>837</v>
+        <v>264</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -11761,7 +11761,7 @@
         <v>10</v>
       </c>
       <c r="F405">
-        <v>815</v>
+        <v>503</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -11781,7 +11781,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>639</v>
+        <v>910</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -11801,7 +11801,7 @@
         <v>10</v>
       </c>
       <c r="F407">
-        <v>291</v>
+        <v>878</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -11821,7 +11821,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>228</v>
+        <v>538</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -11841,7 +11841,7 @@
         <v>10</v>
       </c>
       <c r="F409">
-        <v>220</v>
+        <v>731</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -11861,7 +11861,7 @@
         <v>10</v>
       </c>
       <c r="F410">
-        <v>715</v>
+        <v>837</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -11881,7 +11881,7 @@
         <v>10</v>
       </c>
       <c r="F411">
-        <v>838</v>
+        <v>980</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -11901,7 +11901,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>417</v>
+        <v>499</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -11921,7 +11921,7 @@
         <v>10</v>
       </c>
       <c r="F413">
-        <v>605</v>
+        <v>697</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -11941,7 +11941,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>390</v>
+        <v>475</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -11961,7 +11961,7 @@
         <v>10</v>
       </c>
       <c r="F415">
-        <v>213</v>
+        <v>717</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -11981,7 +11981,7 @@
         <v>10</v>
       </c>
       <c r="F416">
-        <v>409</v>
+        <v>994</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -12001,7 +12001,7 @@
         <v>10</v>
       </c>
       <c r="F417">
-        <v>397</v>
+        <v>534</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -12021,7 +12021,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>319</v>
+        <v>362</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -12041,7 +12041,7 @@
         <v>10</v>
       </c>
       <c r="F419">
-        <v>315</v>
+        <v>780</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>257</v>
+        <v>369</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -12081,7 +12081,7 @@
         <v>10</v>
       </c>
       <c r="F421">
-        <v>584</v>
+        <v>646</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -12101,7 +12101,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -12121,7 +12121,7 @@
         <v>10</v>
       </c>
       <c r="F423">
-        <v>202</v>
+        <v>285</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -12141,7 +12141,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>982</v>
+        <v>986</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -12161,7 +12161,7 @@
         <v>10</v>
       </c>
       <c r="F425">
-        <v>569</v>
+        <v>377</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -12181,7 +12181,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>685</v>
+        <v>837</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -12201,7 +12201,7 @@
         <v>10</v>
       </c>
       <c r="F427">
-        <v>773</v>
+        <v>508</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -12221,7 +12221,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>759</v>
+        <v>744</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -12241,7 +12241,7 @@
         <v>10</v>
       </c>
       <c r="F429">
-        <v>221</v>
+        <v>852</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -12261,7 +12261,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>752</v>
+        <v>781</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -12281,7 +12281,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>918</v>
+        <v>593</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -12301,7 +12301,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>520</v>
+        <v>685</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -12321,7 +12321,7 @@
         <v>10</v>
       </c>
       <c r="F433">
-        <v>593</v>
+        <v>294</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -12341,7 +12341,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>751</v>
+        <v>943</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -12361,7 +12361,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>318</v>
+        <v>383</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -12381,7 +12381,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>858</v>
+        <v>246</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -12401,7 +12401,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>551</v>
+        <v>610</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -12421,7 +12421,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>931</v>
+        <v>730</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -12441,7 +12441,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>323</v>
+        <v>433</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -12461,7 +12461,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>815</v>
+        <v>380</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -12481,7 +12481,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>347</v>
+        <v>448</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -12501,7 +12501,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>767</v>
+        <v>591</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -12521,7 +12521,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>846</v>
+        <v>527</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -12541,7 +12541,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>772</v>
+        <v>225</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -12561,7 +12561,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>991</v>
+        <v>527</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -12581,7 +12581,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>243</v>
+        <v>356</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -12601,7 +12601,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>694</v>
+        <v>472</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -12621,7 +12621,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>963</v>
+        <v>428</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -12641,7 +12641,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>855</v>
+        <v>840</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -12661,7 +12661,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>554</v>
+        <v>834</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -12681,7 +12681,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>317</v>
+        <v>512</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -12701,7 +12701,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>947</v>
+        <v>624</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -12721,7 +12721,7 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>642</v>
+        <v>531</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -12741,7 +12741,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>378</v>
+        <v>666</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -12761,7 +12761,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>712</v>
+        <v>877</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -12781,7 +12781,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>421</v>
+        <v>960</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -12801,7 +12801,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>580</v>
+        <v>952</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -12821,7 +12821,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>956</v>
+        <v>465</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -12841,7 +12841,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>980</v>
+        <v>438</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -12861,7 +12861,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>505</v>
+        <v>290</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -12881,7 +12881,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>905</v>
+        <v>921</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -12901,7 +12901,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>670</v>
+        <v>535</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -12921,7 +12921,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>562</v>
+        <v>600</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -12941,7 +12941,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>967</v>
+        <v>525</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -12961,7 +12961,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>439</v>
+        <v>344</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -12981,7 +12981,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>596</v>
+        <v>366</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -13001,7 +13001,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>350</v>
+        <v>251</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -13021,7 +13021,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>962</v>
+        <v>973</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -13041,7 +13041,7 @@
         <v>10</v>
       </c>
       <c r="F469">
-        <v>688</v>
+        <v>616</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -13061,7 +13061,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>247</v>
+        <v>216</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -13081,7 +13081,7 @@
         <v>10</v>
       </c>
       <c r="F471">
-        <v>698</v>
+        <v>326</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -13101,7 +13101,7 @@
         <v>10</v>
       </c>
       <c r="F472">
-        <v>988</v>
+        <v>634</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -13121,7 +13121,7 @@
         <v>10</v>
       </c>
       <c r="F473">
-        <v>525</v>
+        <v>608</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -13141,7 +13141,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>694</v>
+        <v>832</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -13161,7 +13161,7 @@
         <v>10</v>
       </c>
       <c r="F475">
-        <v>626</v>
+        <v>663</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -13181,7 +13181,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>241</v>
+        <v>757</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -13201,7 +13201,7 @@
         <v>10</v>
       </c>
       <c r="F477">
-        <v>689</v>
+        <v>961</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -13221,7 +13221,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>425</v>
+        <v>924</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -13241,7 +13241,7 @@
         <v>10</v>
       </c>
       <c r="F479">
-        <v>568</v>
+        <v>210</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -13261,7 +13261,7 @@
         <v>10</v>
       </c>
       <c r="F480">
-        <v>808</v>
+        <v>646</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -13281,7 +13281,7 @@
         <v>10</v>
       </c>
       <c r="F481">
-        <v>920</v>
+        <v>894</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -13301,7 +13301,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>511</v>
+        <v>201</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -13321,7 +13321,7 @@
         <v>10</v>
       </c>
       <c r="F483">
-        <v>276</v>
+        <v>311</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -13341,7 +13341,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>407</v>
+        <v>566</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -13361,7 +13361,7 @@
         <v>10</v>
       </c>
       <c r="F485">
-        <v>568</v>
+        <v>825</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -13381,7 +13381,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>926</v>
+        <v>971</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -13401,7 +13401,7 @@
         <v>10</v>
       </c>
       <c r="F487">
-        <v>403</v>
+        <v>461</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -13421,7 +13421,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>885</v>
+        <v>211</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -13441,7 +13441,7 @@
         <v>10</v>
       </c>
       <c r="F489">
-        <v>894</v>
+        <v>546</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -13461,7 +13461,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>633</v>
+        <v>690</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -13481,7 +13481,7 @@
         <v>10</v>
       </c>
       <c r="F491">
-        <v>498</v>
+        <v>729</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -13501,7 +13501,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>469</v>
+        <v>546</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -13521,7 +13521,7 @@
         <v>10</v>
       </c>
       <c r="F493">
-        <v>962</v>
+        <v>737</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -13541,7 +13541,7 @@
         <v>10</v>
       </c>
       <c r="F494">
-        <v>291</v>
+        <v>306</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -13561,7 +13561,7 @@
         <v>10</v>
       </c>
       <c r="F495">
-        <v>404</v>
+        <v>817</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -13581,7 +13581,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>874</v>
+        <v>245</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -13601,7 +13601,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>730</v>
+        <v>339</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -13621,7 +13621,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>539</v>
+        <v>580</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -13641,7 +13641,7 @@
         <v>10</v>
       </c>
       <c r="F499">
-        <v>791</v>
+        <v>764</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -13661,7 +13661,7 @@
         <v>10</v>
       </c>
       <c r="F500">
-        <v>424</v>
+        <v>460</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -13681,7 +13681,7 @@
         <v>10</v>
       </c>
       <c r="F501">
-        <v>238</v>
+        <v>538</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -13701,7 +13701,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>955</v>
+        <v>505</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -13721,7 +13721,7 @@
         <v>10</v>
       </c>
       <c r="F503">
-        <v>237</v>
+        <v>210</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -13741,7 +13741,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>911</v>
+        <v>822</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -13761,7 +13761,7 @@
         <v>10</v>
       </c>
       <c r="F505">
-        <v>334</v>
+        <v>316</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -13781,7 +13781,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>545</v>
+        <v>620</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
@@ -13801,7 +13801,7 @@
         <v>10</v>
       </c>
       <c r="F507">
-        <v>648</v>
+        <v>317</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -13821,7 +13821,7 @@
         <v>10</v>
       </c>
       <c r="F508">
-        <v>219</v>
+        <v>418</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
@@ -13841,7 +13841,7 @@
         <v>10</v>
       </c>
       <c r="F509">
-        <v>710</v>
+        <v>507</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -13861,7 +13861,7 @@
         <v>10</v>
       </c>
       <c r="F510">
-        <v>365</v>
+        <v>457</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
@@ -13881,7 +13881,7 @@
         <v>10</v>
       </c>
       <c r="F511">
-        <v>813</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -13940,7 +13940,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>981</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -13960,7 +13960,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>933</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -13980,7 +13980,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>823</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -14000,7 +14000,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>535</v>
+        <v>815</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -14020,7 +14020,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>359</v>
+        <v>919</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -14040,7 +14040,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>633</v>
+        <v>931</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -14060,7 +14060,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>682</v>
+        <v>961</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -14080,7 +14080,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>213</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -14100,7 +14100,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>833</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -14120,7 +14120,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>704</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -14140,7 +14140,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>223</v>
+        <v>636</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -14160,7 +14160,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>410</v>
+        <v>753</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -14180,7 +14180,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>831</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -14200,7 +14200,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>868</v>
+        <v>835</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -14220,7 +14220,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>678</v>
+        <v>712</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -14240,7 +14240,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>906</v>
+        <v>563</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -14260,7 +14260,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>524</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -14280,7 +14280,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>541</v>
+        <v>837</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -14300,7 +14300,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>285</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -14320,7 +14320,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>631</v>
+        <v>807</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -14340,7 +14340,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>876</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -14360,7 +14360,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>374</v>
+        <v>999</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -14380,7 +14380,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>626</v>
+        <v>487</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -14400,7 +14400,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>352</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -14420,7 +14420,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>268</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -14440,7 +14440,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -14460,7 +14460,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -14480,7 +14480,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>318</v>
+        <v>923</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -14500,7 +14500,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>773</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -14520,7 +14520,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>575</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -14540,7 +14540,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>373</v>
+        <v>558</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -14560,7 +14560,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>321</v>
+        <v>684</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -14580,7 +14580,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>537</v>
+        <v>459</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -14600,7 +14600,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>498</v>
+        <v>439</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -14620,7 +14620,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>243</v>
+        <v>793</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -14640,7 +14640,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>799</v>
+        <v>843</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -14660,7 +14660,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>893</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -14680,7 +14680,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>215</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -14700,7 +14700,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>454</v>
+        <v>387</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -14720,7 +14720,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>534</v>
+        <v>644</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -14740,7 +14740,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>759</v>
+        <v>780</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -14760,7 +14760,7 @@
         <v>10</v>
       </c>
       <c r="F43">
-        <v>848</v>
+        <v>673</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -14780,7 +14780,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>676</v>
+        <v>911</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -14800,7 +14800,7 @@
         <v>10</v>
       </c>
       <c r="F45">
-        <v>980</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -14820,7 +14820,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>857</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -14840,7 +14840,7 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>502</v>
+        <v>405</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -14860,7 +14860,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>317</v>
+        <v>511</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -14880,7 +14880,7 @@
         <v>10</v>
       </c>
       <c r="F49">
-        <v>291</v>
+        <v>368</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -14900,7 +14900,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>498</v>
+        <v>934</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -14920,7 +14920,7 @@
         <v>10</v>
       </c>
       <c r="F51">
-        <v>504</v>
+        <v>599</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -14940,7 +14940,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>629</v>
+        <v>878</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -14960,7 +14960,7 @@
         <v>10</v>
       </c>
       <c r="F53">
-        <v>575</v>
+        <v>605</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -14980,7 +14980,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>750</v>
+        <v>981</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -15000,7 +15000,7 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>910</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -15020,7 +15020,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>492</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -15040,7 +15040,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>870</v>
+        <v>788</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -15060,7 +15060,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -15080,7 +15080,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>489</v>
+        <v>684</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -15100,7 +15100,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>536</v>
+        <v>414</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -15120,7 +15120,7 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>731</v>
+        <v>679</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -15140,7 +15140,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>405</v>
+        <v>953</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -15160,7 +15160,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>537</v>
+        <v>910</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -15180,7 +15180,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>434</v>
+        <v>261</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -15200,7 +15200,7 @@
         <v>10</v>
       </c>
       <c r="F65">
-        <v>789</v>
+        <v>590</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -15220,7 +15220,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>953</v>
+        <v>547</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -15240,7 +15240,7 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>723</v>
+        <v>513</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -15260,7 +15260,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>483</v>
+        <v>409</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -15280,7 +15280,7 @@
         <v>10</v>
       </c>
       <c r="F69">
-        <v>790</v>
+        <v>569</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -15300,7 +15300,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>441</v>
+        <v>382</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -15320,7 +15320,7 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>360</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -15340,7 +15340,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>415</v>
+        <v>356</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -15360,7 +15360,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>478</v>
+        <v>914</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -15380,7 +15380,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>653</v>
+        <v>566</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -15400,7 +15400,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>404</v>
+        <v>966</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -15420,7 +15420,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>495</v>
+        <v>887</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -15440,7 +15440,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>302</v>
+        <v>552</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -15460,7 +15460,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>269</v>
+        <v>625</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -15480,7 +15480,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>300</v>
+        <v>899</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -15500,7 +15500,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>719</v>
+        <v>585</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -15520,7 +15520,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>457</v>
+        <v>565</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -15540,7 +15540,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>479</v>
+        <v>914</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -15560,7 +15560,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>837</v>
+        <v>709</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -15580,7 +15580,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>661</v>
+        <v>382</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -15600,7 +15600,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>908</v>
+        <v>574</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -15620,7 +15620,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>346</v>
+        <v>922</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -15640,7 +15640,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>703</v>
+        <v>769</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -15660,7 +15660,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>990</v>
+        <v>504</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -15680,7 +15680,7 @@
         <v>10</v>
       </c>
       <c r="F89">
-        <v>338</v>
+        <v>554</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -15700,7 +15700,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>778</v>
+        <v>910</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -15720,7 +15720,7 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>255</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -15740,7 +15740,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>266</v>
+        <v>785</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -15760,7 +15760,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>411</v>
+        <v>747</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -15780,7 +15780,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>911</v>
+        <v>471</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -15800,7 +15800,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>445</v>
+        <v>885</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -15820,7 +15820,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>220</v>
+        <v>946</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -15840,7 +15840,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>655</v>
+        <v>616</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -15860,7 +15860,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>279</v>
+        <v>514</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -15880,7 +15880,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>536</v>
+        <v>950</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -15900,7 +15900,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>558</v>
+        <v>904</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -15920,7 +15920,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>507</v>
+        <v>434</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -15940,7 +15940,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -15960,7 +15960,7 @@
         <v>10</v>
       </c>
       <c r="F103">
-        <v>684</v>
+        <v>390</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -15980,7 +15980,7 @@
         <v>10</v>
       </c>
       <c r="F104">
-        <v>342</v>
+        <v>798</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -16000,7 +16000,7 @@
         <v>10</v>
       </c>
       <c r="F105">
-        <v>968</v>
+        <v>834</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -16020,7 +16020,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>901</v>
+        <v>880</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -16040,7 +16040,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>311</v>
+        <v>430</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -16060,7 +16060,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>838</v>
+        <v>767</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -16080,7 +16080,7 @@
         <v>10</v>
       </c>
       <c r="F109">
-        <v>687</v>
+        <v>711</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -16100,7 +16100,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>672</v>
+        <v>642</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -16120,7 +16120,7 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>785</v>
+        <v>947</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -16140,7 +16140,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>414</v>
+        <v>232</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -16160,7 +16160,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>459</v>
+        <v>359</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -16180,7 +16180,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>947</v>
+        <v>351</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -16200,7 +16200,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>523</v>
+        <v>833</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -16220,7 +16220,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>899</v>
+        <v>916</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -16240,7 +16240,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>221</v>
+        <v>877</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -16260,7 +16260,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>744</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -16280,7 +16280,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>408</v>
+        <v>381</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -16300,7 +16300,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>520</v>
+        <v>945</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -16320,7 +16320,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>265</v>
+        <v>917</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -16340,7 +16340,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>253</v>
+        <v>719</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -16360,7 +16360,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>867</v>
+        <v>939</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -16380,7 +16380,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>281</v>
+        <v>983</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -16400,7 +16400,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>776</v>
+        <v>612</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -16420,7 +16420,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>786</v>
+        <v>551</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -16440,7 +16440,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>566</v>
+        <v>806</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -16460,7 +16460,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>444</v>
+        <v>312</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -16480,7 +16480,7 @@
         <v>10</v>
       </c>
       <c r="F129">
-        <v>448</v>
+        <v>435</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -16500,7 +16500,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>685</v>
+        <v>526</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -16520,7 +16520,7 @@
         <v>10</v>
       </c>
       <c r="F131">
-        <v>747</v>
+        <v>338</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -16540,7 +16540,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>613</v>
+        <v>508</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -16560,7 +16560,7 @@
         <v>10</v>
       </c>
       <c r="F133">
-        <v>493</v>
+        <v>613</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -16580,7 +16580,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>337</v>
+        <v>874</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -16600,7 +16600,7 @@
         <v>10</v>
       </c>
       <c r="F135">
-        <v>754</v>
+        <v>784</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -16620,7 +16620,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>778</v>
+        <v>894</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -16640,7 +16640,7 @@
         <v>10</v>
       </c>
       <c r="F137">
-        <v>689</v>
+        <v>521</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -16660,7 +16660,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>870</v>
+        <v>622</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -16680,7 +16680,7 @@
         <v>10</v>
       </c>
       <c r="F139">
-        <v>643</v>
+        <v>722</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -16700,7 +16700,7 @@
         <v>10</v>
       </c>
       <c r="F140">
-        <v>943</v>
+        <v>743</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -16720,7 +16720,7 @@
         <v>10</v>
       </c>
       <c r="F141">
-        <v>854</v>
+        <v>497</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -16740,7 +16740,7 @@
         <v>10</v>
       </c>
       <c r="F142">
-        <v>989</v>
+        <v>999</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -16760,7 +16760,7 @@
         <v>10</v>
       </c>
       <c r="F143">
-        <v>643</v>
+        <v>553</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -16780,7 +16780,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>786</v>
+        <v>536</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -16800,7 +16800,7 @@
         <v>10</v>
       </c>
       <c r="F145">
-        <v>556</v>
+        <v>570</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -16820,7 +16820,7 @@
         <v>10</v>
       </c>
       <c r="F146">
-        <v>796</v>
+        <v>771</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -16840,7 +16840,7 @@
         <v>10</v>
       </c>
       <c r="F147">
-        <v>790</v>
+        <v>681</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -16860,7 +16860,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>987</v>
+        <v>427</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -16880,7 +16880,7 @@
         <v>10</v>
       </c>
       <c r="F149">
-        <v>724</v>
+        <v>520</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -16900,7 +16900,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -16920,7 +16920,7 @@
         <v>10</v>
       </c>
       <c r="F151">
-        <v>244</v>
+        <v>202</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -16940,7 +16940,7 @@
         <v>10</v>
       </c>
       <c r="F152">
-        <v>714</v>
+        <v>431</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -16960,7 +16960,7 @@
         <v>10</v>
       </c>
       <c r="F153">
-        <v>298</v>
+        <v>849</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -16980,7 +16980,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>278</v>
+        <v>673</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -17000,7 +17000,7 @@
         <v>10</v>
       </c>
       <c r="F155">
-        <v>838</v>
+        <v>982</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -17020,7 +17020,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>577</v>
+        <v>683</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -17040,7 +17040,7 @@
         <v>10</v>
       </c>
       <c r="F157">
-        <v>632</v>
+        <v>670</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -17060,7 +17060,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>444</v>
+        <v>278</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -17080,7 +17080,7 @@
         <v>10</v>
       </c>
       <c r="F159">
-        <v>668</v>
+        <v>599</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -17100,7 +17100,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>457</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -17120,7 +17120,7 @@
         <v>10</v>
       </c>
       <c r="F161">
-        <v>467</v>
+        <v>259</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -17140,7 +17140,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>214</v>
+        <v>303</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -17160,7 +17160,7 @@
         <v>10</v>
       </c>
       <c r="F163">
-        <v>881</v>
+        <v>671</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -17180,7 +17180,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>992</v>
+        <v>827</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -17200,7 +17200,7 @@
         <v>10</v>
       </c>
       <c r="F165">
-        <v>829</v>
+        <v>258</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -17220,7 +17220,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -17240,7 +17240,7 @@
         <v>10</v>
       </c>
       <c r="F167">
-        <v>583</v>
+        <v>494</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -17260,7 +17260,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>900</v>
+        <v>807</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -17280,7 +17280,7 @@
         <v>10</v>
       </c>
       <c r="F169">
-        <v>727</v>
+        <v>482</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -17300,7 +17300,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>686</v>
+        <v>356</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -17320,7 +17320,7 @@
         <v>10</v>
       </c>
       <c r="F171">
-        <v>237</v>
+        <v>443</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -17340,7 +17340,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>867</v>
+        <v>294</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -17360,7 +17360,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>397</v>
+        <v>723</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -17380,7 +17380,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>868</v>
+        <v>620</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -17400,7 +17400,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>336</v>
+        <v>567</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -17420,7 +17420,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>572</v>
+        <v>616</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -17440,7 +17440,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>398</v>
+        <v>377</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -17460,7 +17460,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>394</v>
+        <v>870</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -17480,7 +17480,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>832</v>
+        <v>463</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -17500,7 +17500,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>397</v>
+        <v>522</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -17520,7 +17520,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>494</v>
+        <v>365</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -17540,7 +17540,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>457</v>
+        <v>211</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -17560,7 +17560,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>596</v>
+        <v>685</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -17580,7 +17580,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>613</v>
+        <v>253</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -17600,7 +17600,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>294</v>
+        <v>674</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -17620,7 +17620,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>527</v>
+        <v>258</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -17640,7 +17640,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>659</v>
+        <v>402</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -17660,7 +17660,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>962</v>
+        <v>784</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -17680,7 +17680,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>499</v>
+        <v>205</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -17700,7 +17700,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>255</v>
+        <v>771</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -17720,7 +17720,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>384</v>
+        <v>415</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -17740,7 +17740,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>431</v>
+        <v>406</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -17760,7 +17760,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>887</v>
+        <v>483</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -17780,7 +17780,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>858</v>
+        <v>399</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -17800,7 +17800,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>452</v>
+        <v>936</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -17820,7 +17820,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>886</v>
+        <v>978</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -17840,7 +17840,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>958</v>
+        <v>920</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -17860,7 +17860,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>360</v>
+        <v>431</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -17880,7 +17880,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>449</v>
+        <v>957</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -17900,7 +17900,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>832</v>
+        <v>248</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -17920,7 +17920,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>939</v>
+        <v>559</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -17940,7 +17940,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>310</v>
+        <v>587</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -17960,7 +17960,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>285</v>
+        <v>444</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -17980,7 +17980,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>637</v>
+        <v>261</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -18000,7 +18000,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>687</v>
+        <v>292</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -18020,7 +18020,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>382</v>
+        <v>837</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -18040,7 +18040,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>961</v>
+        <v>530</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -18060,7 +18060,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>279</v>
+        <v>803</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -18080,7 +18080,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>276</v>
+        <v>922</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -18100,7 +18100,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>801</v>
+        <v>511</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -18120,7 +18120,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>534</v>
+        <v>442</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -18140,7 +18140,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>857</v>
+        <v>231</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -18160,7 +18160,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>820</v>
+        <v>616</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -18180,7 +18180,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>799</v>
+        <v>660</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -18200,7 +18200,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>573</v>
+        <v>553</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -18220,7 +18220,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>599</v>
+        <v>230</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -18240,7 +18240,7 @@
         <v>10</v>
       </c>
       <c r="F217">
-        <v>435</v>
+        <v>413</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -18260,7 +18260,7 @@
         <v>10</v>
       </c>
       <c r="F218">
-        <v>596</v>
+        <v>620</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -18280,7 +18280,7 @@
         <v>10</v>
       </c>
       <c r="F219">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -18300,7 +18300,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>612</v>
+        <v>332</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -18320,7 +18320,7 @@
         <v>10</v>
       </c>
       <c r="F221">
-        <v>763</v>
+        <v>342</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -18340,7 +18340,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>517</v>
+        <v>479</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -18360,7 +18360,7 @@
         <v>10</v>
       </c>
       <c r="F223">
-        <v>782</v>
+        <v>207</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -18380,7 +18380,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>777</v>
+        <v>788</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -18400,7 +18400,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>399</v>
+        <v>425</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -18420,7 +18420,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>964</v>
+        <v>776</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -18440,7 +18440,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>398</v>
+        <v>959</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -18460,7 +18460,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>750</v>
+        <v>831</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -18480,7 +18480,7 @@
         <v>10</v>
       </c>
       <c r="F229">
-        <v>911</v>
+        <v>868</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -18500,7 +18500,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>392</v>
+        <v>571</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -18520,7 +18520,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>308</v>
+        <v>467</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -18540,7 +18540,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>534</v>
+        <v>750</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -18560,7 +18560,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>451</v>
+        <v>297</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -18580,7 +18580,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>665</v>
+        <v>328</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -18600,7 +18600,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>391</v>
+        <v>829</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -18620,7 +18620,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>666</v>
+        <v>950</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -18640,7 +18640,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>770</v>
+        <v>847</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -18660,7 +18660,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>718</v>
+        <v>967</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -18680,7 +18680,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>613</v>
+        <v>968</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -18700,7 +18700,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>767</v>
+        <v>759</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -18720,7 +18720,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>493</v>
+        <v>889</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -18740,7 +18740,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>518</v>
+        <v>281</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -18760,7 +18760,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>822</v>
+        <v>689</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -18780,7 +18780,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>630</v>
+        <v>857</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -18800,7 +18800,7 @@
         <v>10</v>
       </c>
       <c r="F245">
-        <v>862</v>
+        <v>293</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -18820,7 +18820,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>296</v>
+        <v>558</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -18840,7 +18840,7 @@
         <v>10</v>
       </c>
       <c r="F247">
-        <v>806</v>
+        <v>903</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -18860,7 +18860,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>484</v>
+        <v>268</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -18880,7 +18880,7 @@
         <v>10</v>
       </c>
       <c r="F249">
-        <v>720</v>
+        <v>528</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -18900,7 +18900,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>590</v>
+        <v>734</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -18920,7 +18920,7 @@
         <v>10</v>
       </c>
       <c r="F251">
-        <v>468</v>
+        <v>229</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -18940,7 +18940,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>333</v>
+        <v>601</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -18960,7 +18960,7 @@
         <v>10</v>
       </c>
       <c r="F253">
-        <v>327</v>
+        <v>683</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -18980,7 +18980,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>609</v>
+        <v>922</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -19000,7 +19000,7 @@
         <v>10</v>
       </c>
       <c r="F255">
-        <v>638</v>
+        <v>946</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -19020,7 +19020,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>306</v>
+        <v>780</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -19040,7 +19040,7 @@
         <v>10</v>
       </c>
       <c r="F257">
-        <v>657</v>
+        <v>514</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -19060,7 +19060,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>305</v>
+        <v>205</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -19080,7 +19080,7 @@
         <v>10</v>
       </c>
       <c r="F259">
-        <v>594</v>
+        <v>682</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -19100,7 +19100,7 @@
         <v>10</v>
       </c>
       <c r="F260">
-        <v>927</v>
+        <v>433</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -19120,7 +19120,7 @@
         <v>10</v>
       </c>
       <c r="F261">
-        <v>746</v>
+        <v>691</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -19140,7 +19140,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>771</v>
+        <v>725</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -19160,7 +19160,7 @@
         <v>10</v>
       </c>
       <c r="F263">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -19180,7 +19180,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>998</v>
+        <v>830</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -19200,7 +19200,7 @@
         <v>10</v>
       </c>
       <c r="F265">
-        <v>723</v>
+        <v>987</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -19220,7 +19220,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>214</v>
+        <v>947</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -19240,7 +19240,7 @@
         <v>10</v>
       </c>
       <c r="F267">
-        <v>579</v>
+        <v>970</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -19260,7 +19260,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>564</v>
+        <v>737</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -19280,7 +19280,7 @@
         <v>10</v>
       </c>
       <c r="F269">
-        <v>636</v>
+        <v>394</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -19300,7 +19300,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>547</v>
+        <v>861</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -19320,7 +19320,7 @@
         <v>10</v>
       </c>
       <c r="F271">
-        <v>933</v>
+        <v>468</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -19340,7 +19340,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>996</v>
+        <v>669</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -19360,7 +19360,7 @@
         <v>10</v>
       </c>
       <c r="F273">
-        <v>749</v>
+        <v>396</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -19380,7 +19380,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>995</v>
+        <v>449</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -19400,7 +19400,7 @@
         <v>10</v>
       </c>
       <c r="F275">
-        <v>747</v>
+        <v>478</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -19420,7 +19420,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>465</v>
+        <v>544</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -19440,7 +19440,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>892</v>
+        <v>222</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -19460,7 +19460,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>387</v>
+        <v>595</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -19480,7 +19480,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>543</v>
+        <v>983</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -19500,7 +19500,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>404</v>
+        <v>681</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -19520,7 +19520,7 @@
         <v>10</v>
       </c>
       <c r="F281">
-        <v>651</v>
+        <v>268</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -19540,7 +19540,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>739</v>
+        <v>298</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -19560,7 +19560,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>825</v>
+        <v>770</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -19580,7 +19580,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>394</v>
+        <v>497</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -19600,7 +19600,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>656</v>
+        <v>862</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -19620,7 +19620,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>722</v>
+        <v>318</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -19640,7 +19640,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>712</v>
+        <v>732</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -19660,7 +19660,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>814</v>
+        <v>492</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -19680,7 +19680,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>602</v>
+        <v>367</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -19700,7 +19700,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>804</v>
+        <v>828</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -19720,7 +19720,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>967</v>
+        <v>344</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -19740,7 +19740,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>624</v>
+        <v>906</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -19760,7 +19760,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>358</v>
+        <v>384</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -19780,7 +19780,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>750</v>
+        <v>660</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -19800,7 +19800,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>622</v>
+        <v>755</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -19820,7 +19820,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>713</v>
+        <v>875</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -19840,7 +19840,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>815</v>
+        <v>252</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -19860,7 +19860,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>258</v>
+        <v>507</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -19880,7 +19880,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>417</v>
+        <v>591</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -19900,7 +19900,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>206</v>
+        <v>347</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -19920,7 +19920,7 @@
         <v>10</v>
       </c>
       <c r="F301">
-        <v>201</v>
+        <v>584</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -19940,7 +19940,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>995</v>
+        <v>751</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -19960,7 +19960,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>292</v>
+        <v>822</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -19980,7 +19980,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>422</v>
+        <v>528</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -20000,7 +20000,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>714</v>
+        <v>773</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -20020,7 +20020,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>538</v>
+        <v>269</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -20040,7 +20040,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -20060,7 +20060,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -20080,7 +20080,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>839</v>
+        <v>345</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -20100,7 +20100,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>517</v>
+        <v>620</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -20120,7 +20120,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>904</v>
+        <v>719</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -20140,7 +20140,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>929</v>
+        <v>731</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -20160,7 +20160,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>997</v>
+        <v>257</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -20180,7 +20180,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>710</v>
+        <v>888</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -20200,7 +20200,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>583</v>
+        <v>767</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -20220,7 +20220,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>732</v>
+        <v>386</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -20240,7 +20240,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>340</v>
+        <v>253</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -20260,7 +20260,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>486</v>
+        <v>288</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -20280,7 +20280,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>601</v>
+        <v>946</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -20300,7 +20300,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>265</v>
+        <v>847</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -20320,7 +20320,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>864</v>
+        <v>390</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -20340,7 +20340,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>356</v>
+        <v>261</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -20360,7 +20360,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>307</v>
+        <v>371</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -20380,7 +20380,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>852</v>
+        <v>911</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -20400,7 +20400,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>207</v>
+        <v>950</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -20420,7 +20420,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>257</v>
+        <v>717</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -20440,7 +20440,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>205</v>
+        <v>228</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -20460,7 +20460,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>837</v>
+        <v>842</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -20480,7 +20480,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>494</v>
+        <v>355</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -20500,7 +20500,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>708</v>
+        <v>238</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -20520,7 +20520,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>480</v>
+        <v>777</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -20540,7 +20540,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>289</v>
+        <v>383</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -20560,7 +20560,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>971</v>
+        <v>479</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -20580,7 +20580,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>940</v>
+        <v>392</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -20600,7 +20600,7 @@
         <v>10</v>
       </c>
       <c r="F335">
-        <v>500</v>
+        <v>969</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -20620,7 +20620,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>666</v>
+        <v>211</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -20640,7 +20640,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>200</v>
+        <v>948</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -20660,7 +20660,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>896</v>
+        <v>341</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -20680,7 +20680,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>976</v>
+        <v>612</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -20700,7 +20700,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>748</v>
+        <v>616</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -20720,7 +20720,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>230</v>
+        <v>810</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -20740,7 +20740,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>353</v>
+        <v>701</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -20760,7 +20760,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>550</v>
+        <v>809</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -20780,7 +20780,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>622</v>
+        <v>968</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -20800,7 +20800,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>953</v>
+        <v>539</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -20820,7 +20820,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>820</v>
+        <v>748</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -20840,7 +20840,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>922</v>
+        <v>365</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -20860,7 +20860,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>756</v>
+        <v>857</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -20880,7 +20880,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>464</v>
+        <v>346</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -20900,7 +20900,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>612</v>
+        <v>790</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -20920,7 +20920,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>813</v>
+        <v>693</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -20940,7 +20940,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>264</v>
+        <v>951</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -20960,7 +20960,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>371</v>
+        <v>242</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -20980,7 +20980,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>655</v>
+        <v>932</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -21000,7 +21000,7 @@
         <v>10</v>
       </c>
       <c r="F355">
-        <v>811</v>
+        <v>952</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -21020,7 +21020,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>391</v>
+        <v>648</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -21040,7 +21040,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>222</v>
+        <v>402</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -21060,7 +21060,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>955</v>
+        <v>504</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -21080,7 +21080,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>738</v>
+        <v>973</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -21100,7 +21100,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>960</v>
+        <v>581</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -21120,7 +21120,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>754</v>
+        <v>762</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -21140,7 +21140,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>640</v>
+        <v>956</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -21160,7 +21160,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>871</v>
+        <v>337</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -21180,7 +21180,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>757</v>
+        <v>839</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -21200,7 +21200,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>520</v>
+        <v>672</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -21220,7 +21220,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>602</v>
+        <v>554</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -21240,7 +21240,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>951</v>
+        <v>520</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -21260,7 +21260,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>501</v>
+        <v>675</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -21280,7 +21280,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>302</v>
+        <v>920</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -21300,7 +21300,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>829</v>
+        <v>615</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -21320,7 +21320,7 @@
         <v>10</v>
       </c>
       <c r="F371">
-        <v>423</v>
+        <v>517</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -21340,7 +21340,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>333</v>
+        <v>568</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -21360,7 +21360,7 @@
         <v>10</v>
       </c>
       <c r="F373">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -21380,7 +21380,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>981</v>
+        <v>768</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -21400,7 +21400,7 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>976</v>
+        <v>386</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -21420,7 +21420,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>334</v>
+        <v>522</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -21440,7 +21440,7 @@
         <v>10</v>
       </c>
       <c r="F377">
-        <v>268</v>
+        <v>556</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -21460,7 +21460,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>786</v>
+        <v>750</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -21480,7 +21480,7 @@
         <v>10</v>
       </c>
       <c r="F379">
-        <v>663</v>
+        <v>357</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -21500,7 +21500,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>251</v>
+        <v>898</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -21520,7 +21520,7 @@
         <v>10</v>
       </c>
       <c r="F381">
-        <v>756</v>
+        <v>559</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -21540,7 +21540,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>826</v>
+        <v>238</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -21560,7 +21560,7 @@
         <v>10</v>
       </c>
       <c r="F383">
-        <v>736</v>
+        <v>623</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -21580,7 +21580,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>322</v>
+        <v>585</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -21600,7 +21600,7 @@
         <v>10</v>
       </c>
       <c r="F385">
-        <v>684</v>
+        <v>315</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -21620,7 +21620,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>423</v>
+        <v>904</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -21640,7 +21640,7 @@
         <v>10</v>
       </c>
       <c r="F387">
-        <v>200</v>
+        <v>408</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -21660,7 +21660,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>411</v>
+        <v>483</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -21680,7 +21680,7 @@
         <v>10</v>
       </c>
       <c r="F389">
-        <v>388</v>
+        <v>488</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -21700,7 +21700,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>601</v>
+        <v>996</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -21720,7 +21720,7 @@
         <v>10</v>
       </c>
       <c r="F391">
-        <v>836</v>
+        <v>482</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -21740,7 +21740,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>798</v>
+        <v>879</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -21760,7 +21760,7 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>656</v>
+        <v>983</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -21780,7 +21780,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>676</v>
+        <v>265</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -21800,7 +21800,7 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>319</v>
+        <v>245</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -21820,7 +21820,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>811</v>
+        <v>268</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -21860,7 +21860,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>221</v>
+        <v>518</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -21880,7 +21880,7 @@
         <v>10</v>
       </c>
       <c r="F399">
-        <v>979</v>
+        <v>275</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -21900,7 +21900,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>845</v>
+        <v>327</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -21920,7 +21920,7 @@
         <v>10</v>
       </c>
       <c r="F401">
-        <v>782</v>
+        <v>308</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -21940,7 +21940,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>406</v>
+        <v>387</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -21960,7 +21960,7 @@
         <v>10</v>
       </c>
       <c r="F403">
-        <v>758</v>
+        <v>251</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -21980,7 +21980,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>837</v>
+        <v>264</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -22000,7 +22000,7 @@
         <v>10</v>
       </c>
       <c r="F405">
-        <v>815</v>
+        <v>503</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -22020,7 +22020,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>639</v>
+        <v>910</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -22040,7 +22040,7 @@
         <v>10</v>
       </c>
       <c r="F407">
-        <v>291</v>
+        <v>878</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -22060,7 +22060,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>228</v>
+        <v>538</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -22080,7 +22080,7 @@
         <v>10</v>
       </c>
       <c r="F409">
-        <v>220</v>
+        <v>731</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -22100,7 +22100,7 @@
         <v>10</v>
       </c>
       <c r="F410">
-        <v>715</v>
+        <v>837</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -22120,7 +22120,7 @@
         <v>10</v>
       </c>
       <c r="F411">
-        <v>838</v>
+        <v>980</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -22140,7 +22140,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>417</v>
+        <v>499</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -22160,7 +22160,7 @@
         <v>10</v>
       </c>
       <c r="F413">
-        <v>605</v>
+        <v>697</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -22180,7 +22180,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>390</v>
+        <v>475</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -22200,7 +22200,7 @@
         <v>10</v>
       </c>
       <c r="F415">
-        <v>213</v>
+        <v>717</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -22220,7 +22220,7 @@
         <v>10</v>
       </c>
       <c r="F416">
-        <v>409</v>
+        <v>994</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -22240,7 +22240,7 @@
         <v>10</v>
       </c>
       <c r="F417">
-        <v>397</v>
+        <v>534</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -22260,7 +22260,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>319</v>
+        <v>362</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -22280,7 +22280,7 @@
         <v>10</v>
       </c>
       <c r="F419">
-        <v>315</v>
+        <v>780</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -22300,7 +22300,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>257</v>
+        <v>369</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -22320,7 +22320,7 @@
         <v>10</v>
       </c>
       <c r="F421">
-        <v>584</v>
+        <v>646</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -22340,7 +22340,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -22360,7 +22360,7 @@
         <v>10</v>
       </c>
       <c r="F423">
-        <v>202</v>
+        <v>285</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -22380,7 +22380,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>982</v>
+        <v>986</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -22400,7 +22400,7 @@
         <v>10</v>
       </c>
       <c r="F425">
-        <v>569</v>
+        <v>377</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -22420,7 +22420,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>685</v>
+        <v>837</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -22440,7 +22440,7 @@
         <v>10</v>
       </c>
       <c r="F427">
-        <v>773</v>
+        <v>508</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -22460,7 +22460,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>759</v>
+        <v>744</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -22480,7 +22480,7 @@
         <v>10</v>
       </c>
       <c r="F429">
-        <v>221</v>
+        <v>852</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -22500,7 +22500,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>752</v>
+        <v>781</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -22520,7 +22520,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>918</v>
+        <v>593</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -22540,7 +22540,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>520</v>
+        <v>685</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -22560,7 +22560,7 @@
         <v>10</v>
       </c>
       <c r="F433">
-        <v>593</v>
+        <v>294</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -22580,7 +22580,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>751</v>
+        <v>943</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -22600,7 +22600,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>318</v>
+        <v>383</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -22620,7 +22620,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>858</v>
+        <v>246</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -22640,7 +22640,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>551</v>
+        <v>610</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -22660,7 +22660,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>931</v>
+        <v>730</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -22680,7 +22680,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>323</v>
+        <v>433</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -22700,7 +22700,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>815</v>
+        <v>380</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -22720,7 +22720,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>347</v>
+        <v>448</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -22740,7 +22740,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>767</v>
+        <v>591</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -22760,7 +22760,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>846</v>
+        <v>527</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -22780,7 +22780,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>772</v>
+        <v>225</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -22800,7 +22800,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>991</v>
+        <v>527</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -22820,7 +22820,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>243</v>
+        <v>356</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -22840,7 +22840,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>694</v>
+        <v>472</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -22860,7 +22860,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>963</v>
+        <v>428</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -22880,7 +22880,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>855</v>
+        <v>840</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -22900,7 +22900,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>554</v>
+        <v>834</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -22920,7 +22920,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>317</v>
+        <v>512</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -22940,7 +22940,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>947</v>
+        <v>624</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -22960,7 +22960,7 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>642</v>
+        <v>531</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -22980,7 +22980,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>378</v>
+        <v>666</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -23000,7 +23000,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>712</v>
+        <v>877</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -23020,7 +23020,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>421</v>
+        <v>960</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -23040,7 +23040,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>580</v>
+        <v>952</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -23060,7 +23060,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>956</v>
+        <v>465</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -23080,7 +23080,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>980</v>
+        <v>438</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -23100,7 +23100,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>505</v>
+        <v>290</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -23120,7 +23120,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>905</v>
+        <v>921</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -23140,7 +23140,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>670</v>
+        <v>535</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -23160,7 +23160,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>562</v>
+        <v>600</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -23180,7 +23180,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>967</v>
+        <v>525</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -23200,7 +23200,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>439</v>
+        <v>344</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -23220,7 +23220,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>596</v>
+        <v>366</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -23240,7 +23240,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>350</v>
+        <v>251</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>962</v>
+        <v>973</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -23280,7 +23280,7 @@
         <v>10</v>
       </c>
       <c r="F469">
-        <v>688</v>
+        <v>616</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -23300,7 +23300,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>247</v>
+        <v>216</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -23320,7 +23320,7 @@
         <v>10</v>
       </c>
       <c r="F471">
-        <v>698</v>
+        <v>326</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -23340,7 +23340,7 @@
         <v>10</v>
       </c>
       <c r="F472">
-        <v>988</v>
+        <v>634</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -23360,7 +23360,7 @@
         <v>10</v>
       </c>
       <c r="F473">
-        <v>525</v>
+        <v>608</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -23380,7 +23380,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>694</v>
+        <v>832</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -23400,7 +23400,7 @@
         <v>10</v>
       </c>
       <c r="F475">
-        <v>626</v>
+        <v>663</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -23420,7 +23420,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>241</v>
+        <v>757</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -23440,7 +23440,7 @@
         <v>10</v>
       </c>
       <c r="F477">
-        <v>689</v>
+        <v>961</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -23460,7 +23460,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>425</v>
+        <v>924</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -23480,7 +23480,7 @@
         <v>10</v>
       </c>
       <c r="F479">
-        <v>568</v>
+        <v>210</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -23500,7 +23500,7 @@
         <v>10</v>
       </c>
       <c r="F480">
-        <v>808</v>
+        <v>646</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -23520,7 +23520,7 @@
         <v>10</v>
       </c>
       <c r="F481">
-        <v>920</v>
+        <v>894</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -23540,7 +23540,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>511</v>
+        <v>201</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -23560,7 +23560,7 @@
         <v>10</v>
       </c>
       <c r="F483">
-        <v>276</v>
+        <v>311</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -23580,7 +23580,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>407</v>
+        <v>566</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -23600,7 +23600,7 @@
         <v>10</v>
       </c>
       <c r="F485">
-        <v>568</v>
+        <v>825</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -23620,7 +23620,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>926</v>
+        <v>971</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -23640,7 +23640,7 @@
         <v>10</v>
       </c>
       <c r="F487">
-        <v>403</v>
+        <v>461</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -23660,7 +23660,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>885</v>
+        <v>211</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -23680,7 +23680,7 @@
         <v>10</v>
       </c>
       <c r="F489">
-        <v>894</v>
+        <v>546</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -23700,7 +23700,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>633</v>
+        <v>690</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -23720,7 +23720,7 @@
         <v>10</v>
       </c>
       <c r="F491">
-        <v>498</v>
+        <v>729</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -23740,7 +23740,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>469</v>
+        <v>546</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -23760,7 +23760,7 @@
         <v>10</v>
       </c>
       <c r="F493">
-        <v>962</v>
+        <v>737</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -23780,7 +23780,7 @@
         <v>10</v>
       </c>
       <c r="F494">
-        <v>291</v>
+        <v>306</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -23800,7 +23800,7 @@
         <v>10</v>
       </c>
       <c r="F495">
-        <v>404</v>
+        <v>817</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -23820,7 +23820,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>874</v>
+        <v>245</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -23840,7 +23840,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>730</v>
+        <v>339</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -23860,7 +23860,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>539</v>
+        <v>580</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -23880,7 +23880,7 @@
         <v>10</v>
       </c>
       <c r="F499">
-        <v>791</v>
+        <v>764</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -23900,7 +23900,7 @@
         <v>10</v>
       </c>
       <c r="F500">
-        <v>424</v>
+        <v>460</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -23920,7 +23920,7 @@
         <v>10</v>
       </c>
       <c r="F501">
-        <v>238</v>
+        <v>538</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -23940,7 +23940,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>955</v>
+        <v>505</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -23960,7 +23960,7 @@
         <v>10</v>
       </c>
       <c r="F503">
-        <v>237</v>
+        <v>210</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -23980,7 +23980,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>911</v>
+        <v>822</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -24000,7 +24000,7 @@
         <v>10</v>
       </c>
       <c r="F505">
-        <v>334</v>
+        <v>316</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -24020,7 +24020,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>545</v>
+        <v>620</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
@@ -24040,7 +24040,7 @@
         <v>10</v>
       </c>
       <c r="F507">
-        <v>648</v>
+        <v>317</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -24060,7 +24060,7 @@
         <v>10</v>
       </c>
       <c r="F508">
-        <v>219</v>
+        <v>418</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
@@ -24080,7 +24080,7 @@
         <v>10</v>
       </c>
       <c r="F509">
-        <v>710</v>
+        <v>507</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -24100,7 +24100,7 @@
         <v>10</v>
       </c>
       <c r="F510">
-        <v>365</v>
+        <v>457</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
@@ -24120,7 +24120,7 @@
         <v>10</v>
       </c>
       <c r="F511">
-        <v>813</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
